--- a/НИР_ЭДО_7стран_и_практика/05_Матрицы/Матрица_7стран_ЭДО_ОТ_практика.xlsx
+++ b/НИР_ЭДО_7стран_и_практика/05_Матрицы/Матрица_7стран_ЭДО_ОТ_практика.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -84,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -92,7 +97,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -469,6 +477,7 @@
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -512,6 +521,11 @@
           <t>Особенность</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка для проверки</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="72" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -554,6 +568,11 @@
           <t>2025: массовый переход Schriftform → Textform в трудовом праве при сохранении Schriftform для увольнения, срочных договоров, Aufhebungsvertrag</t>
         </is>
       </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:32014R0910</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -596,6 +615,11 @@
           <t>Ближайшая к РФ кодификация ЭДО; при этом в ОТ электронный журнал инструктажа прямо разрешён — в отличие от ст. 22.1(3) ТК РФ</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://pravo.by/document/?guid=3871&amp;p0=H10900113</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -638,6 +662,11 @@
           <t>Закон об ЭДО современный, трудовое право консервативно: трудовой договор по‑прежнему мыслится как бумажный; для суда e‑mail без QES «не подан»</t>
         </is>
       </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.paragraf.rs/propisi/zakon_o_elektronskom_dokumentu_elektronskoj_identifikaciji_i_uslugama_od_poverenja_u_elektronskom_poslovanju.html</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -680,6 +709,11 @@
           <t>Самая чёткая в семёрке процессуальная презумпция для квалифицированных услуг (LEC 326.4) при одновременной мягкости судов к pantallazos WhatsApp</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.boe.es/eli/es/l/2020/11/11/6</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -722,6 +756,11 @@
           <t>Двойной слой: континентальный eIDAS и англосаксонский non‑discrimination ECA 2000; суды принимают click‑wrap, если условия доведены до пользователя</t>
         </is>
       </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.irishstatutebook.ie/eli/2000/act/27/section/9/enacted/en/html</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -764,6 +803,11 @@
           <t>Самая жёсткая в ЕС‑четвёрке связка «презумпция = только QES». Cass. 5.03.2026 прямо запретила перекладывать бремя на того, кто отрицает подпись, пока суд не установил, что это QES</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.legalis.net/jurisprudences/cour-de-cassation-civile-ch-civile-3-arret-du-5-mars-2026/</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -806,6 +850,11 @@
           <t>Единственная из семи, где даже «живой» электронный документ может быть отвергнут судом из‑за отсутствия 106B‑сертификата</t>
         </is>
       </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>https://new.kenyalaw.org/akn/ke/judgment/keelc/2025/392/eng@2025-02-06</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="72" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -848,8 +897,23 @@
           <t>Отдельный КЭДО; ст. 22.1(3) выводит журналы инструктажа и акты НС</t>
         </is>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_112701/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -860,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -868,6 +932,7 @@
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -896,6 +961,11 @@
           <t>Сравнение с ст. 22.1(3) ТК РФ</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка для проверки</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="72" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -923,6 +993,11 @@
           <t>Отличие: РФ статутно исключает журналы инструктажей и акты НС из КЭДО; Германия такого запрета не знает.</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bundesarbeitsgericht.de/entscheidung/1-abr-104-09/</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -950,6 +1025,11 @@
           <t>Ключевое отличие: Беларусь легализовала электронный журнал; РФ исключила его из КЭДО.</t>
         </is>
       </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mintrud.gov.by/uploads/files/MTiSZ-175-po-sost.-na-02.09.2024.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -977,6 +1057,11 @@
           <t>Отличие: остальные формы ОТ в Сербии можно вести электронно; в РФ исключение ст. 22.1(3) бьёт и по журналам, и по актам НС в контуре КЭДО.</t>
         </is>
       </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.paragraf.rs/propisi/zakon-o-bezbednosti-i-zdravlju-na-radu.html</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1004,6 +1089,11 @@
           <t>Отличие: Испания не выводит обучение ОТ из ЭДО законом.</t>
         </is>
       </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.boe.es/buscar/act.php?id=BOE-A-1995-24292</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1031,6 +1121,11 @@
           <t>Отличие: ирландский суд не фетишизирует журнал; российский законодатель сделал журнал/акт НС исключением из КЭДО.</t>
         </is>
       </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bailii.org/ie/cases/IEHC/2024/2024IEHC167.html</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1058,6 +1153,11 @@
           <t>Отличие: Франция не выводит акты НС и журналы из ЭДО законом.</t>
         </is>
       </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.legifrance.gouv.fr/codes/article_lc/LEGIARTI000006903144</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1085,6 +1185,11 @@
           <t>Отличие: в РФ запрет журналов в КЭДО прямой (ст. 22.1(3)); в Кении запрета нет, но судебный вход для e‑записей узкий.</t>
         </is>
       </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>https://new.kenyalaw.org/akn/ke/act/2007/15</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="72" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1112,8 +1217,23 @@
           <t>Национальный запрет носителя, не вытекающий из eIDAS/113‑З</t>
         </is>
       </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_34683/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1124,7 +1244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1134,6 +1254,7 @@
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1172,6 +1293,11 @@
           <t>Аналогия?</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка для проверки</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="72" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -1209,6 +1335,11 @@
           <t>нет</t>
         </is>
       </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bundesgerichtshof.de/SharedDocs/Entscheidungen/DE/Zivilsenate/VIII_ZS/2023/VIII_ZR_155-23.pdf?__blob=publicationFile&amp;v=1</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1246,6 +1377,11 @@
           <t>да</t>
         </is>
       </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bundesarbeitsgericht.de/entscheidung/1-abr-104-09/</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1283,6 +1419,11 @@
           <t>нет</t>
         </is>
       </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>https://zakony-by.com/hozyajstvennyj_protsessualnyj_kodeks_rb/84.htm</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1320,6 +1461,11 @@
           <t>да</t>
         </is>
       </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mintrud.gov.by/uploads/files/MTiSZ-175-po-sost.-na-02.09.2024.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1357,6 +1503,11 @@
           <t>нет</t>
         </is>
       </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.prlegal.rs/filing-a-complaint-via-email-yes-it-is-possible/</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1394,6 +1545,11 @@
           <t>да</t>
         </is>
       </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lexology.com/library/detail.aspx?g=123a20c5-c0a7-425d-8c37-c9892c70dc93</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1431,6 +1587,11 @@
           <t>нет</t>
         </is>
       </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.boe.es/eli/es/l/2020/11/11/6</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="72" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1468,6 +1629,11 @@
           <t>да</t>
         </is>
       </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.boe.es/buscar/act.php?id=BOE-A-1995-24292</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="72" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1505,6 +1671,11 @@
           <t>нет</t>
         </is>
       </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bailii.org/ie/cases/IEHC/2010/H47.html</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="72" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1542,6 +1713,11 @@
           <t>да</t>
         </is>
       </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bailii.org/ie/cases/IEHC/2024/2024IEHC167.html</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="72" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1579,6 +1755,11 @@
           <t>нет</t>
         </is>
       </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.legalis.net/jurisprudences/cour-de-cassation-civile-ch-civile-3-arret-du-5-mars-2026/</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="72" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1616,6 +1797,11 @@
           <t>да</t>
         </is>
       </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>https://ogletree.fr/publications/od-flash-resiliation-judiciaire-du-contrat-de-travail-et-accident-du-travail-charge-de-la-preuve-en-cas-de-manquement-de-lemployeur-aux-regles-de-prevention-et-de-securite/</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="72" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1653,6 +1839,11 @@
           <t>нет</t>
         </is>
       </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>https://new.kenyalaw.org/akn/ke/judgment/keelc/2025/392/eng@2025-02-06</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="72" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1690,8 +1881,29 @@
           <t>да</t>
         </is>
       </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>https://sheriahub.com/cases/ke/caselaw/bigot-flowers-kenya-ltd-v-cheboswony-employment-and-labour-relations-appeal-10of-2018-2022-keelrc-3772-klr-10may-2022-judgment.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1710,7 +1922,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Легенда пакета семи стран</t>
         </is>
